--- a/data/trans_camb/LAWTONB_2R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 8,44</t>
+          <t>-3,92; 8,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 4,83</t>
+          <t>-8,3; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 16,09</t>
+          <t>2,74; 15,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,3</t>
+          <t>0,01; 11,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 9,23</t>
+          <t>-2,47; 9,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 23,13</t>
+          <t>12,64; 23,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 8,13</t>
+          <t>-0,13; 8,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,42</t>
+          <t>-2,45; 5,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 19,2</t>
+          <t>11,41; 19,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 33,72</t>
+          <t>-13,22; 32,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 18,77</t>
+          <t>-25,53; 19,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 62,9</t>
+          <t>8,29; 59,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 35,51</t>
+          <t>-0,21; 34,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 28,34</t>
+          <t>-6,35; 28,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 70,64</t>
+          <t>32,64; 72,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 26,2</t>
+          <t>-0,32; 26,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 17,47</t>
+          <t>-7,29; 18,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,52; 64,36</t>
+          <t>32,23; 63,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 11,91</t>
+          <t>-9,12; 12,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 3,62</t>
+          <t>-14,11; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 7,43</t>
+          <t>-8,23; 8,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 18,05</t>
+          <t>-11,89; 18,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 18,76</t>
+          <t>-6,99; 19,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 4,81</t>
+          <t>-30,05; 4,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 10,25</t>
+          <t>-7,19; 11,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 9,61</t>
+          <t>-5,72; 9,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 3,84</t>
+          <t>-16,06; 4,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 111,74</t>
+          <t>-44,8; 122,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,76; 36,52</t>
+          <t>-62,31; 28,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 72,7</t>
+          <t>-35,1; 86,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 128,79</t>
+          <t>-40,85; 131,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 146,58</t>
+          <t>-23,35; 137,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,93; 29,44</t>
+          <t>-83,97; 27,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 75,21</t>
+          <t>-31,61; 83,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 77,45</t>
+          <t>-23,61; 78,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 23,16</t>
+          <t>-65,7; 24,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-38,77; -0,92</t>
+          <t>-38,44; 0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 3,31</t>
+          <t>-33,74; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 2,93</t>
+          <t>-31,56; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 4,98</t>
+          <t>-46,39; 4,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 6,12</t>
+          <t>-43,1; 7,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,85; -4,0</t>
+          <t>-42,58; -2,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -2,64</t>
+          <t>-34,23; -3,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 0,68</t>
+          <t>-32,22; -0,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -3,73</t>
+          <t>-29,92; -3,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,98</t>
+          <t>-100,0; 45,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,35; 43,07</t>
+          <t>-85,91; 58,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 24,75</t>
+          <t>-74,19; 17,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,37; 29,98</t>
+          <t>-86,91; 19,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 30,15</t>
+          <t>-78,12; 34,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,25; -12,75</t>
+          <t>-71,8; -6,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,86; -3,04</t>
+          <t>-84,88; -0,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,45; 6,31</t>
+          <t>-76,88; 7,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,66; -18,89</t>
+          <t>-65,87; -15,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,5</t>
+          <t>-5,02; 5,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -0,35</t>
+          <t>-10,5; -0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,56</t>
+          <t>-6,14; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 9,74</t>
+          <t>-1,24; 9,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,13</t>
+          <t>-3,44; 6,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 8,79</t>
+          <t>-19,69; 8,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,93</t>
+          <t>-1,37; 6,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 1,99</t>
+          <t>-5,09; 2,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 4,37</t>
+          <t>-13,6; 4,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 27,87</t>
+          <t>-17,45; 23,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,87; -1,39</t>
+          <t>-36,01; -0,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 15,12</t>
+          <t>-20,42; 16,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 30,24</t>
+          <t>-3,44; 28,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 19,58</t>
+          <t>-9,24; 20,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 26,25</t>
+          <t>-52,32; 24,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 20,67</t>
+          <t>-4,11; 20,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 7,02</t>
+          <t>-15,49; 7,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 14,45</t>
+          <t>-42,93; 13,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>17,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,18</t>
+          <t>14,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 8,93</t>
+          <t>-4,43; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,84</t>
+          <t>-7,88; 4,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 15,29</t>
+          <t>2,97; 15,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 11,24</t>
+          <t>-0,23; 11,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 9,05</t>
+          <t>-2,23; 9,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 23,08</t>
+          <t>12,56; 22,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 8,18</t>
+          <t>-0,29; 8,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,81</t>
+          <t>-2,78; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,13</t>
+          <t>10,78; 18,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 32,97</t>
+          <t>-14,11; 33,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 19,83</t>
+          <t>-23,99; 17,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 59,62</t>
+          <t>9,21; 62,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 34,58</t>
+          <t>-0,51; 35,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 28,23</t>
+          <t>-5,68; 31,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 72,33</t>
+          <t>32,92; 71,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 26,86</t>
+          <t>-0,5; 27,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 18,92</t>
+          <t>-8,26; 18,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,23; 63,84</t>
+          <t>30,28; 60,7</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 12,1</t>
+          <t>-9,55; 11,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 2,76</t>
+          <t>-13,83; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 8,21</t>
+          <t>-9,81; 7,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 18,71</t>
+          <t>-11,35; 18,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 19,69</t>
+          <t>-6,48; 20,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 4,44</t>
+          <t>-9,67; 13,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 11,15</t>
+          <t>-7,65; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,89</t>
+          <t>-5,52; 9,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 4,19</t>
+          <t>-6,3; 7,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-39,77%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,07%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 122,5</t>
+          <t>-44,66; 113,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,31; 28,26</t>
+          <t>-61,09; 46,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 86,36</t>
+          <t>-40,12; 74,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 131,38</t>
+          <t>-38,15; 126,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 137,0</t>
+          <t>-24,29; 160,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,97; 27,99</t>
+          <t>-30,06; 113,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 83,72</t>
+          <t>-32,73; 73,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 78,76</t>
+          <t>-25,23; 62,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 24,04</t>
+          <t>-26,09; 59,07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,46</t>
+          <t>-12,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-22,09</t>
+          <t>-22,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-15,58</t>
+          <t>-16,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 0,89</t>
+          <t>-38,32; -2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 4,69</t>
+          <t>-32,37; 3,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 1,91</t>
+          <t>-30,61; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 4,33</t>
+          <t>-47,58; 4,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 7,6</t>
+          <t>-45,04; 6,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,58; -2,01</t>
+          <t>-43,68; -3,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,23; -3,07</t>
+          <t>-35,14; -3,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,22; -0,56</t>
+          <t>-30,71; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -3,44</t>
+          <t>-29,74; -3,97</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,77%</t>
+          <t>-45,98%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,32%</t>
+          <t>-52,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-47,41%</t>
+          <t>-49,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,13</t>
+          <t>-100,0; 29,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,91; 58,44</t>
+          <t>-87,65; 40,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 17,49</t>
+          <t>-73,42; 28,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,91; 19,38</t>
+          <t>-87,99; 28,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 34,97</t>
+          <t>-82,0; 30,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -6,86</t>
+          <t>-71,98; -9,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,88; -0,84</t>
+          <t>-85,26; -6,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 7,78</t>
+          <t>-76,11; 8,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,87; -15,37</t>
+          <t>-67,02; -16,5</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>2,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,44</t>
+          <t>-5,03; 5,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -0,15</t>
+          <t>-10,3; -0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 3,58</t>
+          <t>-7,06; 2,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 9,04</t>
+          <t>-1,45; 9,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 6,69</t>
+          <t>-4,25; 6,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 8,11</t>
+          <t>2,3; 11,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,11</t>
+          <t>-1,46; 6,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,27</t>
+          <t>-5,44; 2,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 4,19</t>
+          <t>-0,03; 6,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>-6,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,67%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,82%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 23,0</t>
+          <t>-17,24; 26,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,01; -0,59</t>
+          <t>-34,27; -2,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 16,01</t>
+          <t>-23,24; 10,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 28,47</t>
+          <t>-3,76; 29,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 20,92</t>
+          <t>-11,3; 21,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 24,08</t>
+          <t>6,0; 36,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 20,78</t>
+          <t>-4,21; 22,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 7,74</t>
+          <t>-16,55; 6,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 13,8</t>
+          <t>-0,03; 23,11</t>
         </is>
       </c>
     </row>
